--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" state="visible" r:id="rId3"/>
@@ -20,6 +20,9 @@
     <sheet name="会话" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="日志" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="菜单" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="接口" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="页面" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="组件" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -153,6 +156,9 @@
     <t xml:space="preserve">描述</t>
   </si>
   <si>
+    <t xml:space="preserve">关联表</t>
+  </si>
+  <si>
     <t xml:space="preserve">系统</t>
   </si>
   <si>
@@ -162,6 +168,9 @@
     <t xml:space="preserve">菜单</t>
   </si>
   <si>
+    <t xml:space="preserve">菜单表</t>
+  </si>
+  <si>
     <t xml:space="preserve">操作编号</t>
   </si>
   <si>
@@ -178,6 +187,15 @@
   </si>
   <si>
     <t xml:space="preserve">访问</t>
+  </si>
+  <si>
+    <t xml:space="preserve">创建</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">删除</t>
   </si>
   <si>
     <t xml:space="preserve">权限编号</t>
@@ -259,6 +277,12 @@
     <t xml:space="preserve">上级编号</t>
   </si>
   <si>
+    <t xml:space="preserve">图标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">排序</t>
+  </si>
+  <si>
     <t xml:space="preserve">是否可见</t>
   </si>
   <si>
@@ -290,6 +314,69 @@
   </si>
   <si>
     <t xml:space="preserve">菜单管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口地址</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接口类型(get,post,put,delete)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对外接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否白名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件类型1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件类型2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组件类型3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文本框</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">滑动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按钮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下拉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收起</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展开</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文本域</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表格</t>
   </si>
 </sst>
 </file>
@@ -375,7 +462,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -385,6 +472,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -646,19 +737,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -696,22 +787,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,10 +810,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -730,13 +821,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -755,107 +846,286 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="G1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>51</v>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>52</v>
+      <c r="B3" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>53</v>
+      <c r="B4" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>54</v>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>56</v>
+      <c r="C7" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>60</v>
+      <c r="C8" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,6 +1381,9 @@
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1119,23 +1392,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1155,18 +1432,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1177,31 +1454,64 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>28</v>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>29</v>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1226,19 +1536,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1249,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -1262,16 +1572,16 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1302,7 +1612,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" state="visible" r:id="rId3"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t xml:space="preserve">用户联系方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系统用户</t>
   </si>
   <si>
     <r>
@@ -244,6 +247,9 @@
   </si>
   <si>
     <t xml:space="preserve">操作后数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作人</t>
   </si>
   <si>
     <t xml:space="preserve">创建会话1</t>
@@ -737,19 +743,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -782,27 +788,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -810,10 +819,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -821,13 +830,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -851,25 +860,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -880,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -888,7 +897,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -896,7 +905,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -904,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -912,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -920,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -928,7 +937,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -936,7 +945,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -944,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -952,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -979,22 +988,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
@@ -1021,10 +1030,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1048,28 +1057,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>3</v>
@@ -1077,55 +1086,55 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1144,7 +1153,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1163,23 +1172,35 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1259,13 +1280,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1276,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -1290,10 +1311,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -1323,7 +1344,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1372,16 +1393,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1392,10 +1413,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
@@ -1407,10 +1428,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>5</v>
@@ -1437,13 +1458,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1454,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -1465,7 +1486,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -1476,7 +1497,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>5</v>
@@ -1487,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>5</v>
@@ -1498,7 +1519,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>5</v>
@@ -1509,7 +1530,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>5</v>
@@ -1536,19 +1557,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1559,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -1576,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
@@ -1609,10 +1630,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,6 +23,7 @@
     <sheet name="接口" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="页面" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="组件" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="系统分层" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="128">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -383,6 +384,117 @@
   </si>
   <si>
     <t xml:space="preserve">表格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请求对象参数封装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来源于前端页面或接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由控制层接收并自动封装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有验证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无计算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据传输对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">封装前端请求对象参数，来源于控制层功服务层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由服务层或业务层接收</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无验证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">业务对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来源于数据传输对象参数或其他业务对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在服务层内流转</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有计算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持久化对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来源于业务对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在仓储层使用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">页面显示对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">来源于BO或DTO或PO对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由控制层返回</t>
+  </si>
+  <si>
+    <t xml:space="preserve">视图层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展示数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">将数据封装成Request需要数据结构发送给控制层，接收控制层VO对象并用对应组件显示数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">控制层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接收前端参数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">封装为Request对象同转转换为DTO传给服务层，接收返回的DTO封装成VO给前端</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接收DTO对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对业务流程进行处理，并调用其他服务层，转换DTO为BO对象对业务进行处理，将BO转为PO进行持久化操作，将BO或PO转为DTO返回给控制层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过切面处理BO转PO并保存</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仓储层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接收PO对象</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保存数据到数据库</t>
   </si>
 </sst>
 </file>
@@ -810,7 +922,7 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="3" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1148,6 +1260,177 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B3:G14"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="116.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.21"/>
+  </cols>
+  <sheetData>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="127">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -482,10 +482,7 @@
     <t xml:space="preserve">接收DTO对象</t>
   </si>
   <si>
-    <t xml:space="preserve">对业务流程进行处理，并调用其他服务层，转换DTO为BO对象对业务进行处理，将BO转为PO进行持久化操作，将BO或PO转为DTO返回给控制层</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过切面处理BO转PO并保存</t>
+    <t xml:space="preserve">对业务流程进行处理，并调用其他服务层，转换DTO为BO对象对业务进行处理，将BO或PO转为VO返回给控制层</t>
   </si>
   <si>
     <t xml:space="preserve">仓储层</t>
@@ -494,7 +491,7 @@
     <t xml:space="preserve">接收PO对象</t>
   </si>
   <si>
-    <t xml:space="preserve">保存数据到数据库</t>
+    <t xml:space="preserve">接BO转换为PO保存数据到数据库</t>
   </si>
 </sst>
 </file>
@@ -1268,156 +1265,153 @@
   <dimension ref="B3:G14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="116.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="116.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="24.21"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="0" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="C14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="D14" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="129">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -404,6 +404,9 @@
     <t xml:space="preserve">无计算</t>
   </si>
   <si>
+    <t xml:space="preserve">不需要序列化</t>
+  </si>
+  <si>
     <t xml:space="preserve">DTO</t>
   </si>
   <si>
@@ -417,6 +420,9 @@
   </si>
   <si>
     <t xml:space="preserve">无验证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">需要序列化</t>
   </si>
   <si>
     <t xml:space="preserve">BO</t>
@@ -1262,12 +1268,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B3:G14"/>
+  <dimension ref="B3:H14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="116.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.02"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1289,129 +1296,144 @@
       <c r="G3" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="H4" s="0" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="H6" s="0" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="H7" s="0" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="146">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -157,24 +157,57 @@
     <t xml:space="preserve">名称</t>
   </si>
   <si>
+    <t xml:space="preserve">类型</t>
+  </si>
+  <si>
     <t xml:space="preserve">描述</t>
   </si>
   <si>
+    <t xml:space="preserve">上级编号</t>
+  </si>
+  <si>
     <t xml:space="preserve">关联表</t>
   </si>
   <si>
+    <t xml:space="preserve">标识符</t>
+  </si>
+  <si>
     <t xml:space="preserve">系统</t>
   </si>
   <si>
     <t xml:space="preserve">本系统</t>
   </si>
   <si>
+    <t xml:space="preserve">system:system</t>
+  </si>
+  <si>
     <t xml:space="preserve">菜单</t>
   </si>
   <si>
     <t xml:space="preserve">菜单表</t>
   </si>
   <si>
+    <t xml:space="preserve">system:menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按钮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system:button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system:directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system:API</t>
+  </si>
+  <si>
     <t xml:space="preserve">操作编号</t>
   </si>
   <si>
@@ -187,19 +220,37 @@
     <t xml:space="preserve">登录</t>
   </si>
   <si>
+    <t xml:space="preserve">login</t>
+  </si>
+  <si>
     <t xml:space="preserve">注销</t>
   </si>
   <si>
+    <t xml:space="preserve">logout</t>
+  </si>
+  <si>
     <t xml:space="preserve">访问</t>
   </si>
   <si>
+    <t xml:space="preserve">access</t>
+  </si>
+  <si>
     <t xml:space="preserve">创建</t>
   </si>
   <si>
+    <t xml:space="preserve">create</t>
+  </si>
+  <si>
     <t xml:space="preserve">更新</t>
   </si>
   <si>
+    <t xml:space="preserve">update</t>
+  </si>
+  <si>
     <t xml:space="preserve">删除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delete</t>
   </si>
   <si>
     <t xml:space="preserve">权限编号</t>
@@ -281,9 +332,6 @@
     <t xml:space="preserve">删除会话1</t>
   </si>
   <si>
-    <t xml:space="preserve">上级编号</t>
-  </si>
-  <si>
     <t xml:space="preserve">图标</t>
   </si>
   <si>
@@ -338,6 +386,12 @@
     <t xml:space="preserve">是否白名</t>
   </si>
   <si>
+    <t xml:space="preserve">路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登录页</t>
+  </si>
+  <si>
     <t xml:space="preserve">组件编号</t>
   </si>
   <si>
@@ -360,9 +414,6 @@
   </si>
   <si>
     <t xml:space="preserve">滑动</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按钮</t>
   </si>
   <si>
     <t xml:space="preserve">提交</t>
@@ -858,19 +909,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -908,25 +959,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -934,10 +985,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -945,13 +996,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -981,19 +1032,19 @@
         <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -1004,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1012,7 +1063,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1020,7 +1071,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1028,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1036,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1044,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1052,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1060,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1068,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1076,7 +1127,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1106,19 +1157,19 @@
         <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
@@ -1140,7 +1191,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1149,6 +1200,20 @@
       </c>
       <c r="B1" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1172,28 +1237,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>3</v>
@@ -1201,55 +1266,55 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1274,166 +1339,166 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="116.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="31.02"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>97</v>
+        <v>113</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>103</v>
+        <v>113</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>103</v>
+        <v>125</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>103</v>
+        <v>113</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1687,8 +1752,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.58"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1704,6 +1772,15 @@
         <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1712,13 +1789,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1727,13 +1809,52 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1752,20 +1873,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1774,9 +1898,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1785,9 +1912,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1796,9 +1926,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1807,9 +1940,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1818,9 +1954,12 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1829,9 +1968,12 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1856,19 +1998,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1879,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -1896,7 +2038,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
@@ -1932,7 +2074,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>

--- a/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
+++ b/vskeddemos/mavenproject/rbacdemo/rbac0/RBAC0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="账号" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,9 @@
     <sheet name="接口" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="页面" sheetId="14" state="visible" r:id="rId16"/>
     <sheet name="组件" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="系统分层" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="字典类型" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="字典数据" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="系统分层" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="179">
   <si>
     <t xml:space="preserve">账号编号</t>
   </si>
@@ -56,6 +58,9 @@
   </si>
   <si>
     <t xml:space="preserve">user1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">账号是用户登录的基础，如用户名密码</t>
   </si>
   <si>
     <t xml:space="preserve">用户编号</t>
@@ -114,6 +119,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">用户是指使用本系统的人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一个用户只会对就一个账号，一个账号仅会关联一个用户</t>
+  </si>
+  <si>
     <t xml:space="preserve">角色编号</t>
   </si>
   <si>
@@ -151,6 +162,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">角色是指拥有不同权限的集合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一个用户可以有多个角色，一个角色也会被多个用户持有</t>
+  </si>
+  <si>
     <t xml:space="preserve">编号</t>
   </si>
   <si>
@@ -169,6 +186,15 @@
     <t xml:space="preserve">关联表</t>
   </si>
   <si>
+    <t xml:space="preserve">资源ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资源辅助ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">资源扩展唯一标识</t>
+  </si>
+  <si>
     <t xml:space="preserve">标识符</t>
   </si>
   <si>
@@ -178,6 +204,15 @@
     <t xml:space="preserve">本系统</t>
   </si>
   <si>
+    <t xml:space="preserve">主键Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组合主键Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其他唯一标识如字符串</t>
+  </si>
+  <si>
     <t xml:space="preserve">system:system</t>
   </si>
   <si>
@@ -196,6 +231,9 @@
     <t xml:space="preserve">system:button</t>
   </si>
   <si>
+    <t xml:space="preserve">系统内的所有表，数据都是资源 ，每种资源都会有唯一标识，标识符+操作符构成权限标识符，通过权限标识符，前端与后台就可以判断是否拥有某种权限</t>
+  </si>
+  <si>
     <t xml:space="preserve">目录</t>
   </si>
   <si>
@@ -235,6 +273,9 @@
     <t xml:space="preserve">access</t>
   </si>
   <si>
+    <t xml:space="preserve">操作是指对资源有什么样的动作，如创建，注册，注销，登录，删除等</t>
+  </si>
+  <si>
     <t xml:space="preserve">创建</t>
   </si>
   <si>
@@ -268,6 +309,12 @@
     <t xml:space="preserve">登录系统</t>
   </si>
   <si>
+    <t xml:space="preserve">资源与操作构成了权限，资源与权限的标识符可以使前端或后台判断用户是否有某种权限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每个角色拥有什么样的权限</t>
+  </si>
+  <si>
     <t xml:space="preserve">会话编号</t>
   </si>
   <si>
@@ -277,10 +324,19 @@
     <t xml:space="preserve">会话用户</t>
   </si>
   <si>
+    <t xml:space="preserve">会话标识</t>
+  </si>
+  <si>
     <t xml:space="preserve">会话开始时间</t>
   </si>
   <si>
     <t xml:space="preserve">最后操作时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">token密钥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户登录成功后会产生一个会话，同时生成一个token，后期用户再访问需要带上这个token</t>
   </si>
   <si>
     <t xml:space="preserve">日志编号</t>
@@ -332,6 +388,9 @@
     <t xml:space="preserve">删除会话1</t>
   </si>
   <si>
+    <t xml:space="preserve">系统中所有操作都会被记录日志，且日志不能进行修改，删除操作，只能进行查询操作</t>
+  </si>
+  <si>
     <t xml:space="preserve">图标</t>
   </si>
   <si>
@@ -350,6 +409,9 @@
     <t xml:space="preserve">会话管理</t>
   </si>
   <si>
+    <t xml:space="preserve">用户能看到的菜单列表</t>
+  </si>
+  <si>
     <t xml:space="preserve">资源管理</t>
   </si>
   <si>
@@ -386,12 +448,18 @@
     <t xml:space="preserve">是否白名</t>
   </si>
   <si>
+    <t xml:space="preserve">系统内有哪些接口，这些接口是本系统用，还是给第三方用</t>
+  </si>
+  <si>
     <t xml:space="preserve">路径</t>
   </si>
   <si>
     <t xml:space="preserve">登录页</t>
   </si>
   <si>
+    <t xml:space="preserve">系统中有哪些页面，未来可以做管理</t>
+  </si>
+  <si>
     <t xml:space="preserve">组件编号</t>
   </si>
   <si>
@@ -422,6 +490,9 @@
     <t xml:space="preserve">普通</t>
   </si>
   <si>
+    <t xml:space="preserve">一个页面中有哪些组件，未来可以管理</t>
+  </si>
+  <si>
     <t xml:space="preserve">下拉</t>
   </si>
   <si>
@@ -435,6 +506,36 @@
   </si>
   <si>
     <t xml:space="preserve">表格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">启用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">禁用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系统中通用的数据字典</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字典类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">标签</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字典值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">字典名称</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否默认值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据字典中的具体数据</t>
   </si>
   <si>
     <t xml:space="preserve">Request</t>
@@ -843,8 +944,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32.31"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -886,6 +990,11 @@
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -904,26 +1013,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="74.62"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -936,6 +1052,14 @@
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J3" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -954,30 +1078,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -985,10 +1109,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -996,13 +1120,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1021,30 +1148,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.66"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -1055,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1063,7 +1193,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1071,7 +1201,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1079,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1087,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1095,7 +1228,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1103,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1119,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1127,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1279,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.74"/>
@@ -1154,25 +1287,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="0" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1191,29 +1329,43 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30.51"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>92</v>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="0" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1232,89 +1384,98 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32.31"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="3" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="3" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1333,6 +1494,113 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="0" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="0" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K5" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L6" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,标准"&amp;12&amp;Kffffff页 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B3:H14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1344,161 +1612,161 @@
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1517,18 +1785,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.47"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1539,7 +1810,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1551,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
@@ -1562,10 +1833,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1584,12 +1858,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="46.78"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1618,6 +1895,9 @@
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1636,21 +1916,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="25.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1661,10 +1942,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -1675,13 +1956,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1700,15 +1984,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46.78"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1734,6 +2021,9 @@
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1752,35 +2042,46 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="124.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1789,18 +2090,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1809,52 +2119,58 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>33</v>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>35</v>
+      <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>37</v>
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1873,21 +2189,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1898,10 +2214,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
@@ -1912,10 +2228,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1926,13 +2242,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>46</v>
+        <v>57</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1940,10 +2259,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>5</v>
@@ -1954,10 +2273,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>50</v>
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>5</v>
@@ -1968,10 +2287,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>52</v>
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>5</v>
@@ -1993,24 +2312,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="72.11"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -2021,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -2038,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
@@ -2048,6 +2370,11 @@
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J4" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2066,15 +2393,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -2100,6 +2427,9 @@
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
